--- a/artfynd/A 42664-2024 artfynd.xlsx
+++ b/artfynd/A 42664-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119796600</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 42664-2024 artfynd.xlsx
+++ b/artfynd/A 42664-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121150344</v>
       </c>
       <c r="B3" t="n">
-        <v>91988</v>
+        <v>91998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42664-2024 artfynd.xlsx
+++ b/artfynd/A 42664-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121150344</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42664-2024 artfynd.xlsx
+++ b/artfynd/A 42664-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121150344</v>
       </c>
       <c r="B3" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 42664-2024 artfynd.xlsx
+++ b/artfynd/A 42664-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121150344</v>
       </c>
       <c r="B3" t="n">
-        <v>92011</v>
+        <v>92014</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
